--- a/упровление проэктами ЛБ3.xlsx
+++ b/упровление проэктами ЛБ3.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C233B17A-C688-43EA-9EF6-C42CC28BC962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE1F8513-5A42-49DE-A762-16451293F1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <r>
       <rPr>
@@ -57,13 +57,16 @@
     <t>Данные</t>
   </si>
   <si>
+    <t>средний показатель</t>
+  </si>
+  <si>
     <t>Операции</t>
   </si>
   <si>
     <t>Улучшения</t>
   </si>
   <si>
-    <t>среднее использование интернет-данных в игре Brawl Stars —  около 20–25 МБ в час.</t>
+    <t>время запуска</t>
   </si>
   <si>
     <t>Прогресс в игре.</t>
@@ -72,13 +75,19 @@
     <t>Оптимизация маршрута подключения</t>
   </si>
   <si>
-    <t xml:space="preserve">обновляет информацию об ивентах, новых героях, скинах и настройках. Обычно процесс занимает от 10 до 30 секунд на стабильном устройстве и соединении. </t>
+    <t xml:space="preserve">поиск мача </t>
   </si>
   <si>
     <t>Данные о движении в реальном времениф</t>
   </si>
   <si>
-    <t>Выбор сервера</t>
+    <t xml:space="preserve">Выборать другие сервера </t>
+  </si>
+  <si>
+    <t xml:space="preserve">время я игры </t>
+  </si>
+  <si>
+    <t xml:space="preserve">врем до нового  события </t>
   </si>
 </sst>
 </file>
@@ -185,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -203,9 +212,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -218,13 +224,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -278,7 +296,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="az-Cyrl-AZ"/>
-              <a:t>Данные</a:t>
+              <a:t>Время</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -320,6 +338,9 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>Сек</c:v>
+          </c:tx>
           <c:dPt>
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
@@ -334,6 +355,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-73CF-47B4-A5E3-E0839172F9B6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -349,40 +375,191 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000008-73CF-47B4-A5E3-E0839172F9B6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
-          <c:cat>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-73CF-47B4-A5E3-E0839172F9B6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.35027873618264055"/>
+                  <c:y val="0.18338614707100778"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-73CF-47B4-A5E3-E0839172F9B6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.2157655082868008"/>
+                  <c:y val="-1.0078720013864411E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-73CF-47B4-A5E3-E0839172F9B6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="9.4465424713491147E-2"/>
+                  <c:y val="9.0265635695417051E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:separator>, </c:separator>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-73CF-47B4-A5E3-E0839172F9B6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:separator>, </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
             <c:numRef>
-              <c:f>Лист1!$B$3:$B$4</c:f>
+              <c:f>Лист1!$B$3:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>25</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Лист1!$B$3:$B$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>25</c:v>
+                <c:pt idx="2">
+                  <c:v>600</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>30</c:v>
+                <c:pt idx="3">
+                  <c:v>3600</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E5A7-4E93-AE91-0D57F8E41C3C}"/>
+              <c16:uniqueId val="{00000005-73CF-47B4-A5E3-E0839172F9B6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -407,6 +584,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.4782667666817632E-2"/>
+          <c:y val="0.80168457711638375"/>
+          <c:w val="0.28102657380593382"/>
+          <c:h val="7.4257945479587334E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1037,15 +1224,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:colOff>409575</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1373,72 +1560,86 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" customWidth="1"/>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="29.25" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="11"/>
     </row>
-    <row r="2" spans="1:7" ht="16.5">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="9" t="s">
+      <c r="B2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="8"/>
-    </row>
-    <row r="3" spans="1:7" ht="62.25" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="D2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="11">
-        <v>25</v>
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" spans="1:7" ht="54.75" customHeight="1">
+      <c r="A3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="10">
+        <v>18</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>6</v>
+      <c r="D3" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="4"/>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:7" ht="87.75" customHeight="1">
-      <c r="A4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="11">
-        <v>30</v>
-      </c>
-      <c r="C4" s="10" t="s">
+    <row r="4" spans="1:7" ht="74.25" customHeight="1">
+      <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="B4" s="10">
+        <v>6</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="D4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="15"/>
       <c r="F4" s="6"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7">
-      <c r="E5" s="7"/>
+    <row r="5" spans="1:7" ht="30.75">
+      <c r="A5" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="18">
+        <v>600</v>
+      </c>
+      <c r="E5" s="15"/>
     </row>
-    <row r="6" spans="1:7">
-      <c r="E6" s="7"/>
+    <row r="6" spans="1:7" ht="45.75">
+      <c r="A6" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="18">
+        <v>3600</v>
+      </c>
+      <c r="E6" s="15"/>
     </row>
     <row r="8" spans="1:7" ht="15.75">
       <c r="C8" s="1"/>
